--- a/Sample_run/1/student/DuyCNHE187327/TC5/GradeDetail.xlsx
+++ b/Sample_run/1/student/DuyCNHE187327/TC5/GradeDetail.xlsx
@@ -1065,7 +1065,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1124,7 +1124,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1177,7 +1177,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1233,7 +1233,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1292,7 +1292,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1348,7 +1348,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1460,7 +1460,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
         <x:v>59</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1572,7 +1572,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R11" s="4" t="s">
         <x:v>59</x:v>
@@ -1625,7 +1625,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>4000</x:v>
@@ -1684,7 +1684,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R13" s="4" t="s">
         <x:v>59</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="Q14" s="0">
         <x:v>4000</x:v>
@@ -1796,7 +1796,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>47022</x:v>
+        <x:v>33666</x:v>
       </x:c>
       <x:c r="R15" s="4" t="s">
         <x:v>59</x:v>
